--- a/artfynd/A 31895-2025 artfynd.xlsx
+++ b/artfynd/A 31895-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80843374</v>
+        <v>80843356</v>
       </c>
       <c r="B2" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389095.6798411581</v>
+        <v>389024</v>
       </c>
       <c r="R2" t="n">
-        <v>6712124.455854805</v>
+        <v>6712095</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,24 +746,9 @@
           <t>2019-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>grankvist, bålen ser inte helt fräsch ut.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80843356</v>
+        <v>80843305</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389024.216577418</v>
+        <v>388964</v>
       </c>
       <c r="R3" t="n">
-        <v>6712094.637419902</v>
+        <v>6712071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +847,9 @@
           <t>2019-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,12 +880,7 @@
         <v>80843379</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389133.9201145278</v>
+        <v>389134</v>
       </c>
       <c r="R4" t="n">
-        <v>6712180.906721873</v>
+        <v>6712181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +948,9 @@
           <t>2019-11-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,41 +978,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80843338</v>
+        <v>80843374</v>
       </c>
       <c r="B5" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388984.6333575315</v>
+        <v>389096</v>
       </c>
       <c r="R5" t="n">
-        <v>6712122.943730237</v>
+        <v>6712124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,19 +1057,14 @@
           <t>2019-11-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-11-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>grankvist, bålen ser inte helt fräsch ut.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80843377</v>
+        <v>80843330</v>
       </c>
       <c r="B6" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>389095.6798411581</v>
+        <v>388964</v>
       </c>
       <c r="R6" t="n">
-        <v>6712124.455854805</v>
+        <v>6712071</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,19 +1163,9 @@
           <t>2019-11-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,41 +1193,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80843462</v>
+        <v>119012902</v>
       </c>
       <c r="B7" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389601.9829478792</v>
+        <v>388986</v>
       </c>
       <c r="R7" t="n">
-        <v>6712403.456124269</v>
+        <v>6712124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,22 +1269,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fanns på flera ställen i området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,49 +1295,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80843330</v>
+        <v>119013136</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388964.2849830444</v>
+        <v>389123</v>
       </c>
       <c r="R8" t="n">
-        <v>6712070.868369467</v>
+        <v>6712162</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,22 +1375,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På tallar. Flera exemplar,</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,53 +1401,56 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80843305</v>
+        <v>119023404</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1543,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388964.2849830444</v>
+        <v>389765</v>
       </c>
       <c r="R9" t="n">
-        <v>6712070.868369467</v>
+        <v>6712510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,22 +1489,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>fanns fler i området.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,49 +1515,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80843472</v>
+        <v>119028438</v>
       </c>
       <c r="B10" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,13 +1565,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389372.9850500063</v>
+        <v>389612</v>
       </c>
       <c r="R10" t="n">
-        <v>6712319.355673093</v>
+        <v>6712442</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,27 +1595,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På björk.</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,49 +1616,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80843488</v>
+        <v>119028505</v>
       </c>
       <c r="B11" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,13 +1666,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>389283.7352327701</v>
+        <v>389729</v>
       </c>
       <c r="R11" t="n">
-        <v>6712272.349060351</v>
+        <v>6712444</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1810,22 +1696,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,49 +1717,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80843363</v>
+        <v>119028537</v>
       </c>
       <c r="B12" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1896,13 +1767,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>389028.5251359062</v>
+        <v>389714</v>
       </c>
       <c r="R12" t="n">
-        <v>6712074.31102397</v>
+        <v>6712445</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1926,22 +1797,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,49 +1818,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80843481</v>
+        <v>119028606</v>
       </c>
       <c r="B13" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2012,13 +1868,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>389359.1402711548</v>
+        <v>389683</v>
       </c>
       <c r="R13" t="n">
-        <v>6712318.302492158</v>
+        <v>6712445</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2042,22 +1898,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,27 +1919,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119012975</v>
+        <v>119028631</v>
       </c>
       <c r="B14" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,35 +1942,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2137,13 +1969,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388994</v>
+        <v>389618</v>
       </c>
       <c r="R14" t="n">
-        <v>6712116</v>
+        <v>6712437</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2167,12 +1999,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,6 +2013,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2199,15 +2032,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119013664</v>
+        <v>119028665</v>
       </c>
       <c r="B15" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,31 +2043,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2247,13 +2070,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>389221</v>
+        <v>389620</v>
       </c>
       <c r="R15" t="n">
-        <v>6712172</v>
+        <v>6712439</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2277,17 +2100,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på 2 granar..</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,6 +2114,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2314,15 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119013136</v>
+        <v>80843338</v>
       </c>
       <c r="B16" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2357,13 +2171,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>389123</v>
+        <v>388985</v>
       </c>
       <c r="R16" t="n">
-        <v>6712162</v>
+        <v>6712123</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,17 +2201,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tallar. Flera exemplar,</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,27 +2222,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119013030</v>
+        <v>80843363</v>
       </c>
       <c r="B17" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,31 +2245,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2473,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>389020</v>
+        <v>389029</v>
       </c>
       <c r="R17" t="n">
-        <v>6712131</v>
+        <v>6712074</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,52 +2302,43 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack.på tall.</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119023404</v>
+        <v>80843377</v>
       </c>
       <c r="B18" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,33 +2346,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2591,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>389765</v>
+        <v>389096</v>
       </c>
       <c r="R18" t="n">
-        <v>6712510</v>
+        <v>6712124</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,17 +2403,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>fanns fler i området.</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,27 +2424,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119012902</v>
+        <v>80843462</v>
       </c>
       <c r="B19" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,33 +2447,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2710,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388986</v>
+        <v>389602</v>
       </c>
       <c r="R19" t="n">
-        <v>6712124</v>
+        <v>6712403</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2740,17 +2504,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fanns på flera ställen i området.</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2766,60 +2525,49 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119012957</v>
+        <v>80843470</v>
       </c>
       <c r="B20" t="n">
-        <v>5167</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6450</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2827,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388994</v>
+        <v>389529</v>
       </c>
       <c r="R20" t="n">
-        <v>6712116</v>
+        <v>6712413</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,12 +2605,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,71 +2623,52 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119013084</v>
+        <v>80843481</v>
       </c>
       <c r="B21" t="n">
-        <v>97793</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>6450</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2947,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>389056</v>
+        <v>389359</v>
       </c>
       <c r="R21" t="n">
-        <v>6712156</v>
+        <v>6712318</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2977,17 +2706,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>50-tal vid angiven koordinat. Fanns på flera håll i sluttningen.</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,63 +2724,52 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119023422</v>
+        <v>80843488</v>
       </c>
       <c r="B22" t="n">
-        <v>97793</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6450</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3064,13 +2777,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>389785</v>
+        <v>389284</v>
       </c>
       <c r="R22" t="n">
-        <v>6712517</v>
+        <v>6712272</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3094,12 +2807,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,44 +2828,39 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119012855</v>
+        <v>119012975</v>
       </c>
       <c r="B23" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3160,12 +2868,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3178,7 +2890,7 @@
         <v>388994</v>
       </c>
       <c r="R23" t="n">
-        <v>6712082</v>
+        <v>6712116</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3211,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på två granar. Lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,15 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119028505</v>
+        <v>119012855</v>
       </c>
       <c r="B24" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3258,26 +2960,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3285,13 +2992,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>389729</v>
+        <v>388994</v>
       </c>
       <c r="R24" t="n">
-        <v>6712444</v>
+        <v>6712082</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3315,12 +3022,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på två granar. Lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,7 +3041,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3348,15 +3059,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119028606</v>
+        <v>119013030</v>
       </c>
       <c r="B25" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,26 +3070,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3391,13 +3102,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>389683</v>
+        <v>389020</v>
       </c>
       <c r="R25" t="n">
-        <v>6712445</v>
+        <v>6712131</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3421,21 +3132,25 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack.på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3454,15 +3169,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119028631</v>
+        <v>119013664</v>
       </c>
       <c r="B26" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,26 +3180,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3497,13 +3212,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389618</v>
+        <v>389221</v>
       </c>
       <c r="R26" t="n">
-        <v>6712437</v>
+        <v>6712172</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3527,12 +3242,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på 2 granar..</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3541,7 +3261,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3560,42 +3279,43 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119028438</v>
+        <v>119012957</v>
       </c>
       <c r="B27" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3603,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>389612</v>
+        <v>388994</v>
       </c>
       <c r="R27" t="n">
-        <v>6712442</v>
+        <v>6712116</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3633,12 +3353,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,6 +3370,11 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3666,42 +3391,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119028665</v>
+        <v>119013084</v>
       </c>
       <c r="B28" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3709,13 +3438,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>389620</v>
+        <v>389056</v>
       </c>
       <c r="R28" t="n">
-        <v>6712439</v>
+        <v>6712156</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3739,12 +3468,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>50-tal vid angiven koordinat. Fanns på flera håll i sluttningen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3756,6 +3490,11 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3772,15 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119028694</v>
+        <v>119023422</v>
       </c>
       <c r="B29" t="n">
-        <v>97910</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,33 +3522,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3824,13 +3550,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>389706</v>
+        <v>389785</v>
       </c>
       <c r="R29" t="n">
-        <v>6712484</v>
+        <v>6712517</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3887,42 +3613,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119028537</v>
+        <v>119028694</v>
       </c>
       <c r="B30" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3930,13 +3660,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>389714</v>
+        <v>389706</v>
       </c>
       <c r="R30" t="n">
-        <v>6712445</v>
+        <v>6712484</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3990,6 +3720,112 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>80843472</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hundsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>389373</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6712319</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2019-11-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2019-11-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31895-2025 artfynd.xlsx
+++ b/artfynd/A 31895-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843356</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843305</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843379</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843374</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843330</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119012902</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013136</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023404</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028438</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028505</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028537</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028606</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2029,6 +2094,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028631</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028665</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2231,6 +2306,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843338</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843363</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2433,6 +2518,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843377</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2534,6 +2624,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843462</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843470</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2736,6 +2836,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843481</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2837,6 +2942,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843488</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2946,6 +3056,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119012975</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3056,6 +3171,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119012855</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3166,6 +3286,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013030</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3276,6 +3401,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013664</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3388,6 +3518,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119012957</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3508,6 +3643,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013084</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3610,6 +3750,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023422</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3720,6 +3865,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028694</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3826,8 +3976,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80843472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>